--- a/AOR.xlsx
+++ b/AOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iomint.sharepoint.com/teams/CXBIM/Dashboard/Files/PSU/resources/GIS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iomint-my.sharepoint.com/personal/fsadiq_iom_int/Documents/Past/Desktop/FWI Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{F455A17E-974B-44EA-BB00-AFFB54D3F894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF4C42D-8960-400F-B3E9-872CA234BD77}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{F455A17E-974B-44EA-BB00-AFFB54D3F894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22F6F946-F8F4-4118-8928-D60A88CF4FF8}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20201231_Masterlist " sheetId="36" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="141">
   <si>
     <t>New_Camp_SSID</t>
   </si>
@@ -455,16 +455,10 @@
     <t>https://www.humanitarianresponse.info/sites/www.humanitarianresponse.info/files/documents/files/camp_boundary_map_with_drone_image_and_facility_infrastructure_nayapara_rc.pdf</t>
   </si>
   <si>
-    <t>Kutupalong RC*</t>
-  </si>
-  <si>
-    <t>Nayapara RC*</t>
-  </si>
-  <si>
-    <t>Camp 20 Ext</t>
-  </si>
-  <si>
     <t>Camp 4 Ext</t>
+  </si>
+  <si>
+    <t>Camp 20 Extension</t>
   </si>
 </sst>
 </file>
@@ -2691,7 +2685,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
@@ -3338,7 +3332,7 @@
         <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
@@ -3381,7 +3375,7 @@
         <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>57</v>
@@ -3651,7 +3645,7 @@
         <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>77</v>
@@ -3920,12 +3914,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3cb7a4fb-30c9-43e8-85e7-6529e18d9872">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e77b5015-7e61-4ecd-8046-99bc10c1447a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4152,20 +4148,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3cb7a4fb-30c9-43e8-85e7-6529e18d9872">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e77b5015-7e61-4ecd-8046-99bc10c1447a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{753BEFC3-27AE-48C2-B56B-791504EC960C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3C1570B-1C83-400B-B778-E9A1C47CC992}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="ce8551ce-fedd-4656-aa31-7e42f5cef03d"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="537bfee3-272b-47b5-b4fd-2e4b9dac5c55"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="3cb7a4fb-30c9-43e8-85e7-6529e18d9872"/>
+    <ds:schemaRef ds:uri="e77b5015-7e61-4ecd-8046-99bc10c1447a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4190,20 +4195,15 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3C1570B-1C83-400B-B778-E9A1C47CC992}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{753BEFC3-27AE-48C2-B56B-791504EC960C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ce8551ce-fedd-4656-aa31-7e42f5cef03d"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="537bfee3-272b-47b5-b4fd-2e4b9dac5c55"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="3cb7a4fb-30c9-43e8-85e7-6529e18d9872"/>
-    <ds:schemaRef ds:uri="e77b5015-7e61-4ecd-8046-99bc10c1447a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{2059aa38-f392-4105-be92-628035578272}" enabled="1" method="Standard" siteId="{1588262d-23fb-43b4-bd6e-bce49c8e6186}" removed="0"/>
+</clbl:labelList>
 </file>